--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104691_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104691_W26.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1967</v>
+        <v>5.0981</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4623</v>
+        <v>4.7453</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.3528</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9445</v>
+        <v>2.9531</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3216</v>
+        <v>0.3298</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6229</v>
+        <v>2.6232</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4975</v>
+        <v>4.4855</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5451</v>
+        <v>3.5375</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.553</v>
+        <v>-1.5325</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.118</v>
+        <v>1.0069</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9648</v>
+        <v>0.2598</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1532</v>
+        <v>0.7471</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4586</v>
+        <v>3.3157</v>
       </c>
       <c r="E3" t="n">
-        <v>0.474</v>
+        <v>2.3318</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9846</v>
+        <v>0.9839</v>
       </c>
       <c r="G3" t="n">
-        <v>1.367</v>
+        <v>2.6901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8658</v>
+        <v>0.6331</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5011</v>
+        <v>2.057</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7177</v>
+        <v>3.5183</v>
       </c>
       <c r="K3" t="n">
-        <v>1.198</v>
+        <v>0.9643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5197000000000001</v>
+        <v>2.554</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3507</v>
+        <v>-0.8282</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3321</v>
+        <v>-0.3312</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1331</v>
+        <v>1.2207</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3176</v>
+        <v>0.2296</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8155</v>
+        <v>0.9911</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.8603</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0025</v>
+        <v>3.1166</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2117</v>
+        <v>0.5084</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7907999999999999</v>
+        <v>2.6082</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7159</v>
+        <v>1.3639</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6555</v>
+        <v>0.8618</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0604</v>
+        <v>0.502</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5729</v>
+        <v>1.6923</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0035</v>
+        <v>1.1786</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5694</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.857</v>
+        <v>-0.3284</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.348</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.509</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8726</v>
+        <v>1.8014</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0393</v>
+        <v>0.3899</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.4115</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8678</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5274</v>
+        <v>1.3861</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3419</v>
+        <v>0.6028</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8693</v>
+        <v>0.7833</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.1195</v>
+        <v>0.5673</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9422</v>
+        <v>0.1142</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1773</v>
+        <v>0.4532</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.1211</v>
+        <v>0.5799</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6101</v>
+        <v>0.4309</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.511</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9984</v>
+        <v>-0.0125</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6663</v>
+        <v>0.3043</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3177</v>
+        <v>0.9977</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0302</v>
+        <v>0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>1.348</v>
+        <v>0.9747</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4633</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>5.0777</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0663</v>
+        <v>1.3559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5338000000000001</v>
+        <v>-0.328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5325</v>
+        <v>1.6839</v>
       </c>
       <c r="G6" t="n">
-        <v>0.546</v>
+        <v>-4.1252</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1008</v>
+        <v>-0.9448</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4452</v>
+        <v>-3.1805</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5822000000000001</v>
+        <v>-3.1535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4329</v>
+        <v>-0.628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>-2.5255</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0362</v>
+        <v>-0.9717</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2959</v>
+        <v>-0.6549</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7056</v>
+        <v>1.1719</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>0.0414</v>
       </c>
       <c r="U6" t="n">
-        <v>0.754</v>
+        <v>1.1305</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>5.4474</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>5.0604</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2139</v>
+        <v>0.6885</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2764</v>
+        <v>0.8288</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0625</v>
+        <v>-0.1403</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2915</v>
+        <v>-4.2779</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3693</v>
+        <v>-1.0217</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9222</v>
+        <v>-3.2563</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1803</v>
+        <v>-2.0444</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1803</v>
+        <v>-0.3457</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.6987</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1113</v>
+        <v>-2.2335</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1891</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9222</v>
+        <v>-1.5576</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6681</v>
+        <v>0.3809</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4567</v>
+        <v>-0.3466</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2114</v>
+        <v>0.7275</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6105</v>
+        <v>4.3579</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.3579</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1857</v>
+        <v>-0.2149</v>
       </c>
       <c r="E8" t="n">
-        <v>0.299</v>
+        <v>-0.2005</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1133</v>
+        <v>-0.0144</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.2642</v>
+        <v>-1.2874</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0069</v>
+        <v>-0.3732</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.2573</v>
+        <v>-0.9143</v>
       </c>
       <c r="J8" t="n">
-        <v>-2</v>
+        <v>-0.1864</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3126</v>
+        <v>-0.1864</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6874</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2643</v>
+        <v>-1.1011</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6944</v>
+        <v>-0.1868</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5699</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1476</v>
+        <v>0.2287</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9376</v>
+        <v>-0.0141</v>
       </c>
       <c r="U8" t="n">
-        <v>0.79</v>
+        <v>0.2429</v>
       </c>
       <c r="V8" t="n">
-        <v>4.3707</v>
+        <v>0.6162</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3707</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7237</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.236</v>
+        <v>-1.2403</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5123</v>
+        <v>0.5484</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1517</v>
+        <v>-0.1496</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1183</v>
+        <v>-0.0871</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5637</v>
+        <v>-1.1602</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1386</v>
+        <v>0.098</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4251</v>
+        <v>-1.2582</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.547</v>
+        <v>-1.5376</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="J10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.599</v>
+        <v>-1.5893</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2435</v>
+        <v>0.1498</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1905</v>
+        <v>0.0463</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6637</v>
+        <v>-1.2993</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1454</v>
+        <v>0.3168</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8092</v>
+        <v>-1.6161</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7301</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3015</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0316</v>
+        <v>-1.0323</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1938</v>
+        <v>0.1754</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4604</v>
+        <v>0.4514</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.437</v>
+        <v>0.7839</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0484</v>
+        <v>0.1414</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4854</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4413</v>
+        <v>-3.2985</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0118</v>
+        <v>-1.1419</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4295</v>
+        <v>-2.1566</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.181</v>
+        <v>-3.1775</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4834</v>
+        <v>-0.4798</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6975</v>
+        <v>-2.6977</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3293</v>
+        <v>-1.3437</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8516</v>
+        <v>-1.8339</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.075</v>
+        <v>0.058</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3926</v>
+        <v>-0.1438</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9904</v>
+        <v>-3.6729</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9313</v>
+        <v>-4.7339</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9409</v>
+        <v>1.061</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.897</v>
+        <v>-2.8997</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2466</v>
+        <v>-2.2487</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6504</v>
+        <v>-0.651</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8745</v>
+        <v>-1.8976</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4586</v>
+        <v>-1.4726</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0225</v>
+        <v>-1.0022</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0765</v>
+        <v>0.2543</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6705</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.268299999999999</v>
+        <v>4.623099999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>1.743</v>
+        <v>1.7873</v>
       </c>
       <c r="F14" t="n">
-        <v>2.525199999999999</v>
+        <v>2.835899999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.6086</v>
+        <v>-10.6058</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.1453</v>
+        <v>-3.1586</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.463399999999999</v>
+        <v>-7.4476</v>
       </c>
       <c r="J14" t="n">
-        <v>2.148199999999999</v>
+        <v>1.914699999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.669</v>
+        <v>1.5161</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4790999999999998</v>
+        <v>0.3985000000000004</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.757</v>
+        <v>-12.5208</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.8146</v>
+        <v>-4.6747</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.9425</v>
+        <v>-7.845899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1344</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>7.5912</v>
+        <v>7.967099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.04519999999999991</v>
+        <v>0.3216999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>7.6366</v>
+        <v>7.6455</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4198</v>
+        <v>8.400199999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>12.116</v>
+        <v>12.0706</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.696099999999999</v>
+        <v>-3.6702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4349</v>
+        <v>2.057</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8951</v>
+        <v>0.2697</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4602</v>
+        <v>1.7874</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2703</v>
+        <v>2.3398</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3795</v>
+        <v>0.2828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1092</v>
+        <v>2.057</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2429</v>
+        <v>1.5771</v>
       </c>
       <c r="K15" t="n">
-        <v>2.019</v>
+        <v>0.1402</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2239</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0274</v>
+        <v>0.7627</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3605</v>
+        <v>0.1426</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3331</v>
+        <v>0.6201</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7602</v>
+        <v>-0.6469</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8771</v>
+        <v>-0.8506</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8831</v>
+        <v>0.2036</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.5029</v>
+        <v>-0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7712</v>
+        <v>-0.2292</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7317</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2294</v>
+        <v>1.7447</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6212</v>
+        <v>1.263</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6082</v>
+        <v>0.4817</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8652</v>
+        <v>2.4764</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9091</v>
+        <v>1.4158</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7743</v>
+        <v>1.0606</v>
       </c>
       <c r="J16" t="n">
-        <v>2.165</v>
+        <v>2.7614</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.372</v>
+        <v>1.6892</v>
       </c>
       <c r="L16" t="n">
-        <v>3.537</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2998</v>
+        <v>-0.2851</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5371</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2373</v>
+        <v>-0.0116</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.048</v>
+        <v>-0.0487</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4608</v>
+        <v>-0.1326</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4128</v>
+        <v>0.0838</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1082</v>
+        <v>1.4502</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9286</v>
+        <v>0.8038</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1797</v>
+        <v>0.6464</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4735</v>
+        <v>1.8578</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4126</v>
+        <v>-1.9044</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0609</v>
+        <v>3.7622</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7765</v>
+        <v>2.1281</v>
       </c>
       <c r="K17" t="n">
-        <v>1.697</v>
+        <v>-1.3864</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0795</v>
+        <v>3.5145</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.303</v>
+        <v>-0.2703</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2844</v>
+        <v>-0.518</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0186</v>
+        <v>0.2477</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6847</v>
+        <v>-0.8141</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4869</v>
+        <v>-1.2269</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1978</v>
+        <v>0.4127</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.954</v>
+        <v>0.5102</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.141</v>
+        <v>0.2081</v>
       </c>
       <c r="F18" t="n">
-        <v>1.095</v>
+        <v>0.3021</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3667</v>
+        <v>0.2477</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3063</v>
+        <v>0.4249</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0604</v>
+        <v>-0.1772</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6324</v>
+        <v>0.3475</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1825</v>
+        <v>0.3103</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4499</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7343</v>
+        <v>-0.0998</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1238</v>
+        <v>0.1146</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6105</v>
+        <v>-0.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7756</v>
+        <v>-0.1928</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3217</v>
+        <v>-0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.454</v>
+        <v>-0.0534</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2844</v>
+        <v>0.1512</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2099</v>
+        <v>1.0501</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0745</v>
+        <v>-0.8988</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2427</v>
+        <v>2.2714</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4213</v>
+        <v>2.3754</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1786</v>
+        <v>-0.104</v>
       </c>
       <c r="J19" t="n">
-        <v>0.349</v>
+        <v>2.2261</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3117</v>
+        <v>2.0027</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.2234</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1063</v>
+        <v>0.0452</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1096</v>
+        <v>0.3727</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2159</v>
+        <v>-0.3275</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4119</v>
+        <v>0.467</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1391</v>
+        <v>0.0531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2728</v>
+        <v>0.4138</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-3.4976</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.043</v>
+        <v>-0.1724</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8352000000000001</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8782</v>
+        <v>-0.1724</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9792999999999999</v>
+        <v>-0.1724</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6061</v>
+        <v>-0.1724</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3732</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2313</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9382</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2931</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2521</v>
+        <v>-0.1724</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3321</v>
+        <v>-0.1724</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3548</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3962</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5748</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1732</v>
+        <v>-0.4118</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.3335</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1732</v>
+        <v>-0.7453</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1732</v>
+        <v>0.9757</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1732</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.3724</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.2026</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.9201</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.2826</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1732</v>
+        <v>-0.227</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1732</v>
+        <v>-0.3168</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.0898</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.7352</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.8691</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.1339</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5628</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2554</v>
+        <v>-0.8812</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2263</v>
+        <v>-0.4936</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0291</v>
+        <v>-0.3876</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1615</v>
+        <v>2.833</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1615</v>
+        <v>0.3843</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2.4487</v>
       </c>
       <c r="J22" t="n">
-        <v>0.052</v>
+        <v>3.7334</v>
       </c>
       <c r="K22" t="n">
-        <v>0.052</v>
+        <v>1.2615</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.4719</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1096</v>
+        <v>-0.9004</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1096</v>
+        <v>-0.8772</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.0232</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5511</v>
+        <v>-0.9418</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>-1.1084</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2728</v>
+        <v>0.1666</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4866</v>
+        <v>-1.0149</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.802</v>
+        <v>-2.1867</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6847</v>
+        <v>1.1718</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8299</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.375</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4549</v>
+        <v>0.7139</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7664</v>
+        <v>0.7335</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2743</v>
+        <v>-0.0485</v>
       </c>
       <c r="L23" t="n">
-        <v>2.4921</v>
+        <v>0.782</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9365</v>
+        <v>-0.0979</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8993</v>
+        <v>-0.0298</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0372</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5434</v>
+        <v>-1.561</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4608</v>
+        <v>-1.5544</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0066</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6217</v>
+        <v>-1.0672</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2886</v>
+        <v>-0.1087</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6669</v>
+        <v>-0.9585</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6153</v>
+        <v>0.1663</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0911</v>
+        <v>0.1663</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7064</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7419</v>
+        <v>0.0517</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0417</v>
+        <v>0.0517</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7837</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1266</v>
+        <v>0.1146</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0494</v>
+        <v>0.1146</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0772</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1443</v>
+        <v>-0.3717</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6695</v>
+        <v>-0.1604</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4748</v>
+        <v>-0.2113</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0148</v>
+        <v>-1.9832</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0781</v>
+        <v>-3.0128</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0634</v>
+        <v>1.0296</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.501</v>
+        <v>-3.5129</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0433</v>
+        <v>-1.0426</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.4577</v>
+        <v>-2.4703</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9185</v>
+        <v>-2.9557</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8525</v>
+        <v>-0.8693</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5825</v>
+        <v>-0.5573</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4723</v>
+        <v>-1.4216</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5303</v>
+        <v>-1.415</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0581</v>
+        <v>-0.0066</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W25" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6847</v>
+        <v>-3.0782</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4792</v>
+        <v>-0.9624</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2055</v>
+        <v>-2.1158</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4786</v>
+        <v>0.4877</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6998</v>
+        <v>0.7035</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J26" t="n">
-        <v>0.718</v>
+        <v>0.715</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2395</v>
+        <v>-0.2273</v>
       </c>
       <c r="N26" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6345</v>
+        <v>0.2276</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2299</v>
+        <v>-0.2418</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4047</v>
+        <v>0.4694</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.2685</v>
+        <v>-2.695599999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.5252</v>
+        <v>-2.836</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.7432</v>
+        <v>0.1406000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>10.6088</v>
+        <v>10.6061</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1454</v>
+        <v>3.1586</v>
       </c>
       <c r="I27" t="n">
-        <v>7.463400000000001</v>
+        <v>7.447500000000002</v>
       </c>
       <c r="J27" t="n">
-        <v>12.7569</v>
+        <v>12.5207</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8146</v>
+        <v>4.674800000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>7.9425</v>
+        <v>7.846000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.1482</v>
+        <v>-1.915</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.6691</v>
+        <v>-1.5162</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.4790999999999999</v>
+        <v>-0.3987</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1341</v>
+        <v>1.1381</v>
       </c>
       <c r="Q27" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4757</v>
+        <v>12.5197</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.591400000000001</v>
+        <v>-6.039199999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-7.636500000000001</v>
+        <v>-7.6455</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04530000000000001</v>
+        <v>1.6059</v>
       </c>
       <c r="V27" t="n">
-        <v>-8.4198</v>
+        <v>-8.4002</v>
       </c>
       <c r="W27" t="n">
-        <v>3.696</v>
+        <v>3.6703</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.1159</v>
+        <v>-12.0705</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104691_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104691_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.6702</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104691_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-12.0705</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
